--- a/data/Protocols.xlsx
+++ b/data/Protocols.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u050158/django/region/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martijn.bentum/django/region/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C8C728-AF19-2F43-9265-F3B3A6F15328}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5533A34-CD19-D540-B7B8-C1AAEBA618F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="500" windowWidth="19200" windowHeight="21100" tabRatio="921" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="500" windowWidth="19200" windowHeight="21100" tabRatio="921" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Preliminary" sheetId="6" r:id="rId1"/>
     <sheet name="Text" sheetId="1" r:id="rId2"/>
     <sheet name="Publication" sheetId="14" r:id="rId3"/>
-    <sheet name="Publisher" sheetId="13" r:id="rId4"/>
-    <sheet name="Illustration" sheetId="4" r:id="rId5"/>
-    <sheet name="Person" sheetId="2" r:id="rId6"/>
-    <sheet name="Movement" sheetId="11" r:id="rId7"/>
-    <sheet name="Periodical" sheetId="12" r:id="rId8"/>
-    <sheet name="Location" sheetId="10" r:id="rId9"/>
+    <sheet name="Podcast" sheetId="15" r:id="rId4"/>
+    <sheet name="Publisher" sheetId="13" r:id="rId5"/>
+    <sheet name="Illustration" sheetId="4" r:id="rId6"/>
+    <sheet name="Person" sheetId="2" r:id="rId7"/>
+    <sheet name="Movement" sheetId="11" r:id="rId8"/>
+    <sheet name="Periodical" sheetId="12" r:id="rId9"/>
+    <sheet name="Location" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,85 +41,11 @@
   <commentList>
     <comment ref="C32" authorId="0" shapeId="0" xr:uid="{1072B17D-0430-49AB-93A2-2C81446E3E13}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    In onze vorige bespreking (11/11/2020), bespraken we dat dit veld ook gebruikt kan worden als filter. Als we nog geen use permission voor materialen hebben, zorgt Martijn er voor dat die materialen nog niet zichtbaar zijn voor end users. Dat is een mooie oplossing, maar het past bij nader inzien niet bij het origineel bedoelde gebruik van dit veld (zie de beschrijving in het gele veld). Om de filter-optie te kunnen gebruiken, moeten we dit veld anders gaan benaderen.
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>Voorstel: hernoem veld "Use permission" en maak nieuwe beschrijving voor dit veld: "If we have use permission, select 'yes' from the drop-down menu. If we do not have use permission, select 'no' from the drop-down menu. If we do not have use permission but should obtain permission, select 'no - request use permission' from the drop-down menu." Martijn, je kunt beide 'no' opties eruit filteren, zodat ze niet zichtbaar zijn voor end users, toch?</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    In onze vorige bespreking (11/11/2020), bespraken we dat dit veld ook gebruikt kan worden als filter. Als we nog geen use permission voor materialen hebben, zorgt Martijn er voor dat die materialen nog niet zichtbaar zijn voor end users. Dat is een mooie oplossing, maar het past bij nader inzien niet bij het origineel bedoelde gebruik van dit veld (zie de beschrijving in het gele veld). Om de filter-optie te kunnen gebruiken, moeten we dit veld anders gaan benaderen.
+Voorstel: hernoem veld "Use permission" en maak nieuwe beschrijving voor dit veld: "If we have use permission, select 'yes' from the drop-down menu. If we do not have use permission, select 'no' from the drop-down menu. If we do not have use permission but should obtain permission, select 'no - request use permission' from the drop-down menu." Martijn, je kunt beide 'no' opties eruit filteren, zodat ze niet zichtbaar zijn voor end users, toch?</t>
       </text>
     </comment>
   </commentList>
@@ -126,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="149">
   <si>
     <t>Field</t>
   </si>
@@ -577,12 +504,36 @@
   <si>
     <t>Enter the publication date -- year for books and specific month/day for periodicals (e.g.  March 12, 1867 or February 1902).</t>
   </si>
+  <si>
+    <t>Podcast</t>
+  </si>
+  <si>
+    <t>Speakers</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Enter a short description of the podcast</t>
+  </si>
+  <si>
+    <t>Audio link</t>
+  </si>
+  <si>
+    <t>Enter the url link to the audio recording (e.g. youtube)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter the names of the speakers in the podcast (e.g. Mary Smith, Jan Hout, Nancy Dalrimple) </t>
+  </si>
+  <si>
+    <t>Enter the recording date -- year and specific month/day  (e.g.  March 12, 1867 or February 1902).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,12 +571,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -667,7 +612,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -690,24 +635,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -717,9 +647,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -758,9 +685,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -798,7 +725,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -904,7 +831,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1046,7 +973,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1054,20 +981,9 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C24" dT="2020-11-13T08:58:16.33" personId="{C26FBF23-C5AC-4DC8-A7D2-8A64FF201DC5}" id="{1072B17D-0430-49AB-93A2-2C81446E3E13}">
+  <threadedComment ref="C32" dT="2020-11-13T08:58:16.33" personId="{C26FBF23-C5AC-4DC8-A7D2-8A64FF201DC5}" id="{1072B17D-0430-49AB-93A2-2C81446E3E13}">
     <text>In onze vorige bespreking (11/11/2020), bespraken we dat dit veld ook gebruikt kan worden als filter. Als we nog geen use permission voor materialen hebben, zorgt Martijn er voor dat die materialen nog niet zichtbaar zijn voor end users. Dat is een mooie oplossing, maar het past bij nader inzien niet bij het origineel bedoelde gebruik van dit veld (zie de beschrijving in het gele veld). Om de filter-optie te kunnen gebruiken, moeten we dit veld anders gaan benaderen.
 Voorstel: hernoem veld "Use permission" en maak nieuwe beschrijving voor dit veld: "If we have use permission, select 'yes' from the drop-down menu. If we do not have use permission, select 'no' from the drop-down menu. If we do not have use permission but should obtain permission, select 'no - request use permission' from the drop-down menu." Martijn, je kunt beide 'no' opties eruit filteren, zodat ze niet zichtbaar zijn voor end users, toch?</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A14" dT="2020-11-06T09:30:29.22" personId="{C26FBF23-C5AC-4DC8-A7D2-8A64FF201DC5}" id="{F7DBCE83-71A1-4035-AF36-C51DDD929C84}">
-    <text>This is not in the repository (yet)?</text>
-  </threadedComment>
-  <threadedComment ref="B15" dT="2020-11-13T09:09:06.95" personId="{C26FBF23-C5AC-4DC8-A7D2-8A64FF201DC5}" id="{CC94FBC0-0FAC-47EF-A7C6-3205BC49AD30}">
-    <text>Als we de mogelijkheid tot image upload toevoegen, moeten we ook een veld met use permission toevoegen, niet?</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1081,7 +997,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1101,14 +1017,126 @@
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
+      <c r="A5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
+      <c r="A6" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="98.6640625" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.1640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="112" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1234,7 +1262,7 @@
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1245,7 +1273,7 @@
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -1256,7 +1284,7 @@
       <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1267,42 +1295,27 @@
       <c r="A14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B15" s="9"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B16" s="9"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="9"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="9"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="9"/>
-      <c r="D27" s="12"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C31" s="13"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="15"/>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="D27" s="9"/>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C32" s="10"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C33" s="1"/>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C36" s="13"/>
+      <c r="C36" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1322,10 +1335,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1468,7 +1481,7 @@
       <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="13" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1512,6 +1525,84 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E875BC8D-AD00-8947-BAEB-B1F9BB5EA7E1}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27.83203125" customWidth="1"/>
+    <col min="3" max="3" width="50.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B60D439-B579-4EFE-B952-8C9FCC091BF4}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1520,10 +1611,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1587,7 +1678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1624,7 +1715,7 @@
       <c r="B3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="14" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1646,7 +1737,7 @@
       <c r="B5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="11" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1687,7 +1778,7 @@
       <c r="A9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -1723,7 +1814,7 @@
       <c r="B12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="11" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1732,7 +1823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1751,14 +1842,14 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="5" t="s">
         <v>130</v>
       </c>
     </row>
@@ -1895,22 +1986,22 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="15" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="17"/>
+      <c r="D15" s="12"/>
     </row>
     <row r="16" spans="1:4" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -1923,7 +2014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{370B46B3-6EE1-4216-A803-6AF09A06E7EC}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1933,10 +2024,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1996,13 +2087,13 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="13" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2013,7 +2104,7 @@
       <c r="B8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="13" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2022,7 +2113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D925AC44-FF41-4DE4-9EED-0562877DBB84}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2032,51 +2123,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="16" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="16" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="16" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="16" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
@@ -2084,137 +2175,25 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="16" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="13" t="s">
         <v>118</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="98.6640625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9.1640625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
   </sheetData>
